--- a/output/graficos_nacionales/plot_nacional_serie_d_depmayores_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_depmayores_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20 21:39</t>
+    <t xml:space="preserve">2026-08-21 12:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_depmayores_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_depmayores_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-21 12:47</t>
+    <t xml:space="preserve">2026-09-04 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_d_depmayores_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_d_depmayores_a_2020.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 19:53</t>
+    <t xml:space="preserve">2026-09-07 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
